--- a/data/trans_dic/P34B02_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P34B02_R-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, 3 veces por semana o más</t>
+          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 11,57</t>
+          <t>5,0; 11,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,91; 12,57</t>
+          <t>5,67; 12,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,57; 44,58</t>
+          <t>31,81; 46,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 9,86</t>
+          <t>3,69; 9,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 9,47</t>
+          <t>3,3; 9,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,46; 42,75</t>
+          <t>33,57; 43,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 9,69</t>
+          <t>5,05; 9,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,64</t>
+          <t>5,26; 9,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,03; 42,48</t>
+          <t>33,94; 42,42</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 7,47</t>
+          <t>3,44; 7,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,4</t>
+          <t>2,04; 5,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,4; 35,49</t>
+          <t>24,0; 35,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,16</t>
+          <t>0,98; 3,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,75</t>
+          <t>1,8; 4,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 15,4</t>
+          <t>9,52; 15,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,0</t>
+          <t>2,67; 5,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,42</t>
+          <t>2,16; 4,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,74; 24,52</t>
+          <t>17,92; 24,65</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,95</t>
+          <t>1,42; 4,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 7,72</t>
+          <t>3,1; 7,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,03</t>
+          <t>4,0; 10,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,48</t>
+          <t>0,84; 4,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 9,24</t>
+          <t>3,58; 8,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 14,31</t>
+          <t>8,07; 14,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,84</t>
+          <t>1,34; 3,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,52</t>
+          <t>3,9; 7,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 11,12</t>
+          <t>6,81; 11,38</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 10,29</t>
+          <t>4,79; 10,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 10,3</t>
+          <t>4,8; 10,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 11,02</t>
+          <t>4,39; 10,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,45</t>
+          <t>2,35; 6,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,58</t>
+          <t>0,97; 4,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 8,8</t>
+          <t>3,25; 8,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,41</t>
+          <t>4,03; 7,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,46</t>
+          <t>3,2; 6,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 8,59</t>
+          <t>4,15; 8,46</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 7,32</t>
+          <t>1,39; 6,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,13; 17,38</t>
+          <t>7,95; 17,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,23; 27,9</t>
+          <t>15,85; 27,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,38</t>
+          <t>0,92; 5,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,25; 12,73</t>
+          <t>5,34; 12,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,84; 12,62</t>
+          <t>5,95; 13,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,17</t>
+          <t>1,67; 4,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,62; 13,27</t>
+          <t>7,46; 13,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,57; 18,08</t>
+          <t>11,52; 17,97</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,68</t>
+          <t>1,42; 5,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,18; 8,72</t>
+          <t>3,26; 8,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,97</t>
+          <t>2,41; 6,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,82</t>
+          <t>1,11; 5,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,52; 9,18</t>
+          <t>3,55; 9,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,08; 13,36</t>
+          <t>6,93; 13,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,38</t>
+          <t>1,64; 4,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,95; 7,85</t>
+          <t>3,85; 7,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,3</t>
+          <t>5,2; 9,0</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,9</t>
+          <t>2,13; 4,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,92; 11,61</t>
+          <t>6,89; 11,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,24; 19,48</t>
+          <t>12,55; 20,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,65</t>
+          <t>2,46; 5,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,82</t>
+          <t>4,08; 7,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,58; 12,4</t>
+          <t>4,16; 12,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,67</t>
+          <t>2,66; 4,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,99; 8,94</t>
+          <t>5,96; 9,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,18; 14,71</t>
+          <t>7,4; 14,45</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,15; 10,08</t>
+          <t>6,27; 10,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,34; 11,6</t>
+          <t>7,54; 11,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,91; 25,53</t>
+          <t>8,0; 25,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,38</t>
+          <t>3,92; 7,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,14</t>
+          <t>4,68; 8,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,4; 17,24</t>
+          <t>12,48; 17,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,4; 7,96</t>
+          <t>5,47; 7,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,07</t>
+          <t>6,59; 9,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,72; 20,12</t>
+          <t>10,44; 20,15</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,66; 6,25</t>
+          <t>4,66; 6,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,64; 8,53</t>
+          <t>6,66; 8,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,98; 20,41</t>
+          <t>14,31; 20,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,16; 4,53</t>
+          <t>3,19; 4,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 6,22</t>
+          <t>4,62; 6,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,59; 13,86</t>
+          <t>10,43; 13,96</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,09; 5,1</t>
+          <t>4,07; 5,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,82; 6,98</t>
+          <t>5,8; 7,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,31; 16,66</t>
+          <t>13,25; 16,7</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, 3 veces por semana o más</t>
+          <t>Población que realiza gimnasia suave, como juegos que requieren poco esfuerzo y similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14083; 33951</t>
+          <t>14689; 34780</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17352; 36930</t>
+          <t>16659; 37833</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98312; 138853</t>
+          <t>99069; 143546</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10021; 28336</t>
+          <t>10595; 28437</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9748; 27343</t>
+          <t>9532; 27469</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96907; 123813</t>
+          <t>97225; 125795</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28675; 56285</t>
+          <t>29352; 56305</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29712; 56135</t>
+          <t>30620; 56276</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>204565; 255362</t>
+          <t>204025; 255004</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17359; 37771</t>
+          <t>17415; 38246</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10619; 27141</t>
+          <t>10248; 27800</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>126465; 183967</t>
+          <t>124400; 185540</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5981; 21692</t>
+          <t>5139; 19935</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8727; 24854</t>
+          <t>9434; 24601</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50900; 79318</t>
+          <t>49023; 77328</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26591; 51349</t>
+          <t>27437; 52211</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22504; 45363</t>
+          <t>22195; 44919</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>183354; 253382</t>
+          <t>185213; 254679</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4663; 16056</t>
+          <t>4599; 15340</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9262; 24597</t>
+          <t>9863; 24259</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12433; 31713</t>
+          <t>12645; 31725</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3080; 15293</t>
+          <t>2867; 14768</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12169; 31085</t>
+          <t>12029; 30136</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28115; 49892</t>
+          <t>28130; 50850</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9224; 25553</t>
+          <t>8940; 26474</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25446; 49224</t>
+          <t>25511; 48218</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45767; 73925</t>
+          <t>45269; 75642</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17686; 38472</t>
+          <t>17929; 39268</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17386; 38106</t>
+          <t>17762; 38949</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13072; 34285</t>
+          <t>13655; 34115</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9481; 25098</t>
+          <t>9136; 25437</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3866; 17729</t>
+          <t>3747; 17266</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15289; 41840</t>
+          <t>15479; 42119</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30780; 56501</t>
+          <t>30752; 57865</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24278; 48891</t>
+          <t>24269; 49063</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33105; 67623</t>
+          <t>32662; 66524</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3127; 15570</t>
+          <t>2949; 14559</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17176; 36720</t>
+          <t>16783; 36196</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29010; 49877</t>
+          <t>28328; 49006</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1981; 11824</t>
+          <t>2015; 12152</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11482; 27833</t>
+          <t>11673; 27136</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12160; 26283</t>
+          <t>12402; 27113</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7767; 22345</t>
+          <t>7200; 20941</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32734; 57042</t>
+          <t>32078; 57247</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44776; 69979</t>
+          <t>44583; 69543</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3967; 15560</t>
+          <t>3894; 15062</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8378; 22952</t>
+          <t>8569; 22106</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6613; 18783</t>
+          <t>6506; 17395</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2956; 13488</t>
+          <t>3100; 14359</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9622; 25085</t>
+          <t>9699; 25656</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18204; 34349</t>
+          <t>17803; 34669</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8210; 24285</t>
+          <t>9063; 25094</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21188; 42119</t>
+          <t>20628; 41922</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27567; 48994</t>
+          <t>27389; 47421</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13972; 32432</t>
+          <t>14081; 32920</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>45439; 76219</t>
+          <t>45230; 75994</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>76007; 120922</t>
+          <t>77927; 125689</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16536; 39171</t>
+          <t>17048; 38792</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>28690; 54085</t>
+          <t>28190; 54930</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30359; 105141</t>
+          <t>35248; 104333</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36102; 63253</t>
+          <t>36053; 64599</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>80775; 120549</t>
+          <t>80332; 121552</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>105475; 216041</t>
+          <t>108755; 212196</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>47876; 78518</t>
+          <t>48819; 78638</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>57172; 90303</t>
+          <t>58675; 92008</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>73434; 237117</t>
+          <t>74319; 238030</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>33607; 60759</t>
+          <t>32263; 58904</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>38948; 67223</t>
+          <t>38680; 66971</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>88627; 123197</t>
+          <t>89152; 122939</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>86489; 127574</t>
+          <t>87704; 125428</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>102638; 145477</t>
+          <t>105748; 147943</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>159793; 330547</t>
+          <t>171608; 331197</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>159461; 213959</t>
+          <t>159752; 213869</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>225471; 289648</t>
+          <t>226105; 291049</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>483064; 704999</t>
+          <t>494412; 704076</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>112404; 160957</t>
+          <t>113574; 163496</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>160398; 220525</t>
+          <t>163789; 217341</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>387261; 506874</t>
+          <t>381246; 510352</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>285254; 356338</t>
+          <t>284181; 358510</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>404184; 484009</t>
+          <t>402679; 485913</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>946294; 1185050</t>
+          <t>941990; 1187365</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B02_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P34B02_R-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 11,85</t>
+          <t>4,81; 11,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,67; 12,88</t>
+          <t>5,94; 12,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,81; 46,09</t>
+          <t>32,23; 43,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 9,9</t>
+          <t>3,67; 10,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 9,51</t>
+          <t>3,38; 9,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,57; 43,43</t>
+          <t>32,11; 41,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,05; 9,69</t>
+          <t>4,92; 9,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 9,66</t>
+          <t>5,29; 9,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,94; 42,42</t>
+          <t>33,69; 40,81</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 7,57</t>
+          <t>3,48; 7,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,53</t>
+          <t>2,02; 5,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,0; 35,79</t>
+          <t>23,46; 34,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,82</t>
+          <t>1,14; 4,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,7</t>
+          <t>1,75; 4,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 15,02</t>
+          <t>9,52; 14,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,08</t>
+          <t>2,57; 5,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,38</t>
+          <t>2,17; 4,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,92; 24,65</t>
+          <t>17,43; 23,31</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,73</t>
+          <t>1,22; 5,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 7,61</t>
+          <t>3,03; 8,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 10,04</t>
+          <t>4,12; 9,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,33</t>
+          <t>0,69; 4,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,96</t>
+          <t>3,53; 8,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 14,59</t>
+          <t>8,32; 14,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,98</t>
+          <t>1,4; 3,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,36</t>
+          <t>3,72; 7,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 11,38</t>
+          <t>6,78; 10,92</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 10,5</t>
+          <t>4,78; 10,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 10,53</t>
+          <t>4,85; 10,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 10,97</t>
+          <t>4,59; 11,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,54</t>
+          <t>2,07; 6,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,46</t>
+          <t>0,95; 4,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 8,85</t>
+          <t>4,81; 10,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,58</t>
+          <t>4,06; 7,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,48</t>
+          <t>3,16; 6,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 8,46</t>
+          <t>5,18; 9,86</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 6,85</t>
+          <t>1,48; 6,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 17,14</t>
+          <t>8,14; 17,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,85; 27,42</t>
+          <t>18,04; 29,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,53</t>
+          <t>0,91; 5,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,34; 12,41</t>
+          <t>4,98; 12,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,95; 13,02</t>
+          <t>5,66; 12,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,85</t>
+          <t>1,59; 5,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,46; 13,32</t>
+          <t>7,29; 13,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,52; 17,97</t>
+          <t>12,15; 19,09</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,5</t>
+          <t>1,42; 5,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,26; 8,4</t>
+          <t>3,23; 8,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,45</t>
+          <t>2,42; 6,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,13</t>
+          <t>1,11; 5,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,55; 9,39</t>
+          <t>3,7; 9,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,93; 13,49</t>
+          <t>6,9; 12,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,53</t>
+          <t>1,5; 4,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,82</t>
+          <t>3,94; 7,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,0</t>
+          <t>5,16; 8,87</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,97</t>
+          <t>1,97; 4,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,89; 11,57</t>
+          <t>6,89; 11,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,55; 20,25</t>
+          <t>12,41; 19,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,59</t>
+          <t>2,45; 5,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,95</t>
+          <t>4,1; 7,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 12,31</t>
+          <t>9,24; 13,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,76</t>
+          <t>2,58; 4,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,96; 9,02</t>
+          <t>5,92; 9,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,4; 14,45</t>
+          <t>11,45; 15,29</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,27; 10,09</t>
+          <t>6,1; 9,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,54; 11,82</t>
+          <t>7,33; 11,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,0; 25,63</t>
+          <t>22,19; 28,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,15</t>
+          <t>3,94; 7,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,11</t>
+          <t>4,56; 8,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,48; 17,21</t>
+          <t>12,6; 17,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,47; 7,82</t>
+          <t>5,46; 8,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,59; 9,22</t>
+          <t>6,57; 9,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,44; 20,15</t>
+          <t>18,01; 22,02</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,66; 6,24</t>
+          <t>4,63; 6,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,66; 8,57</t>
+          <t>6,65; 8,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14,31; 20,38</t>
+          <t>17,99; 21,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,19; 4,6</t>
+          <t>3,16; 4,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,13</t>
+          <t>4,58; 6,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,43; 13,96</t>
+          <t>12,61; 14,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,07; 5,14</t>
+          <t>4,05; 5,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,8; 7,0</t>
+          <t>5,8; 7,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,25; 16,7</t>
+          <t>15,56; 17,41</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119084</t>
+          <t>119508</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>110272</t>
+          <t>115546</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>229356</t>
+          <t>235054</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14689; 34780</t>
+          <t>14110; 33698</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16659; 37833</t>
+          <t>17449; 36549</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99069; 143546</t>
+          <t>102756; 137988</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10595; 28437</t>
+          <t>10528; 29061</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9532; 27469</t>
+          <t>9769; 26974</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97225; 125795</t>
+          <t>101495; 130856</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29352; 56305</t>
+          <t>28577; 54233</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30620; 56276</t>
+          <t>30794; 56227</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>204025; 255004</t>
+          <t>213903; 259133</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154116</t>
+          <t>150567</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63120</t>
+          <t>66789</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>217237</t>
+          <t>217356</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17415; 38246</t>
+          <t>17596; 38465</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10248; 27800</t>
+          <t>10145; 27181</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>124400; 185540</t>
+          <t>124499; 183277</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5139; 19935</t>
+          <t>5962; 22750</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9434; 24601</t>
+          <t>9153; 25177</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49023; 77328</t>
+          <t>52027; 81289</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27437; 52211</t>
+          <t>26362; 51626</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22195; 44919</t>
+          <t>22215; 46168</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>185213; 254679</t>
+          <t>187752; 251093</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20551</t>
+          <t>19770</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37548</t>
+          <t>39222</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58099</t>
+          <t>58993</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4599; 15340</t>
+          <t>3963; 16339</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9863; 24259</t>
+          <t>9658; 25595</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12645; 31725</t>
+          <t>13030; 30529</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2867; 14768</t>
+          <t>2369; 15199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12029; 30136</t>
+          <t>11873; 29989</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28130; 50850</t>
+          <t>29590; 50821</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8940; 26474</t>
+          <t>9320; 25050</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25511; 48218</t>
+          <t>24390; 48263</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45269; 75642</t>
+          <t>45542; 73329</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21780</t>
+          <t>27509</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27152</t>
+          <t>29423</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>48932</t>
+          <t>56932</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17929; 39268</t>
+          <t>17872; 38876</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17762; 38949</t>
+          <t>17940; 39505</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13655; 34115</t>
+          <t>17063; 42855</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9136; 25437</t>
+          <t>8034; 23915</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3747; 17266</t>
+          <t>3694; 16597</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15479; 42119</t>
+          <t>20300; 42986</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30752; 57865</t>
+          <t>30978; 56329</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24269; 49063</t>
+          <t>23938; 49716</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32662; 66524</t>
+          <t>41090; 78271</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37679</t>
+          <t>47602</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>19297</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>55857</t>
+          <t>66900</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2949; 14559</t>
+          <t>3140; 14501</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16783; 36196</t>
+          <t>17185; 37358</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28328; 49006</t>
+          <t>37108; 61425</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2015; 12152</t>
+          <t>1994; 12031</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11673; 27136</t>
+          <t>10879; 26508</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12402; 27113</t>
+          <t>12828; 27815</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7200; 20941</t>
+          <t>6865; 22082</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32078; 57247</t>
+          <t>31351; 57389</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44583; 69543</t>
+          <t>52545; 82545</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25227</t>
+          <t>25269</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>36531</t>
+          <t>36399</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3894; 15062</t>
+          <t>3903; 15095</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8569; 22106</t>
+          <t>8496; 22204</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6506; 17395</t>
+          <t>6542; 17859</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3100; 14359</t>
+          <t>3106; 14943</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9699; 25656</t>
+          <t>10105; 25942</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17803; 34669</t>
+          <t>18187; 33807</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9063; 25094</t>
+          <t>8283; 24041</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20628; 41922</t>
+          <t>21130; 41874</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27389; 47421</t>
+          <t>27600; 47399</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>98447</t>
+          <t>111141</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73762</t>
+          <t>85819</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>172208</t>
+          <t>196960</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>14081; 32920</t>
+          <t>13030; 32589</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>45230; 75994</t>
+          <t>45233; 75916</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>77927; 125689</t>
+          <t>88740; 137443</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17048; 38792</t>
+          <t>16990; 38554</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>28190; 54930</t>
+          <t>28341; 54347</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35248; 104333</t>
+          <t>71031; 103121</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36053; 64599</t>
+          <t>34955; 64856</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>80332; 121552</t>
+          <t>79780; 122016</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>108755; 212196</t>
+          <t>169867; 226841</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>167923</t>
+          <t>201906</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>104738</t>
+          <t>124155</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>272662</t>
+          <t>326061</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>48819; 78638</t>
+          <t>47509; 77852</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>58675; 92008</t>
+          <t>57095; 90684</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>74319; 238030</t>
+          <t>177107; 230563</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>32263; 58904</t>
+          <t>32483; 60974</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>38680; 66971</t>
+          <t>37661; 66381</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>89152; 122939</t>
+          <t>104460; 148159</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>87704; 125428</t>
+          <t>87444; 128346</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>105748; 147943</t>
+          <t>105495; 147001</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>171608; 331197</t>
+          <t>293070; 358366</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>630884</t>
+          <t>689134</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>459998</t>
+          <t>505520</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1090881</t>
+          <t>1194654</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>159752; 213869</t>
+          <t>158657; 210159</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>226105; 291049</t>
+          <t>225886; 290355</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>494412; 704076</t>
+          <t>634269; 742774</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>113574; 163496</t>
+          <t>112463; 159792</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>163789; 217341</t>
+          <t>162356; 218899</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>381246; 510352</t>
+          <t>470003; 546123</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>284181; 358510</t>
+          <t>282956; 358909</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>402679; 485913</t>
+          <t>402471; 487216</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>941990; 1187365</t>
+          <t>1128587; 1263093</t>
         </is>
       </c>
     </row>
